--- a/apps/web/public/templates/guias-manuais-modelo.xlsx
+++ b/apps/web/public/templates/guias-manuais-modelo.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>cpf</t>
   </si>
@@ -25,6 +25,15 @@
     <t>total_guias</t>
   </si>
   <si>
+    <t>total_consultas</t>
+  </si>
+  <si>
+    <t>total_imobilizacoes</t>
+  </si>
+  <si>
+    <t>total_outros_hospitais</t>
+  </si>
+  <si>
     <t>motivo</t>
   </si>
   <si>
@@ -47,6 +56,33 @@
   </si>
   <si>
     <t>Exceções de procedimento nao cobertas pela regra automatica</t>
+  </si>
+  <si>
+    <t>52998224725</t>
+  </si>
+  <si>
+    <t>Dr. Pedro Infante</t>
+  </si>
+  <si>
+    <t>Guias normais e consultas do mes conferidas a mao - contagem automatica das consultas divergiu</t>
+  </si>
+  <si>
+    <t>15350946056</t>
+  </si>
+  <si>
+    <t>Dr. Vitor Imob</t>
+  </si>
+  <si>
+    <t>Lote de Imobilizacoes conferido a mao - sub-lote nao reconhecido pelo nome</t>
+  </si>
+  <si>
+    <t>12345678909</t>
+  </si>
+  <si>
+    <t>Dra. Marta Hospitais</t>
+  </si>
+  <si>
+    <t>Lote de Outros Hospitais conferido a mao</t>
   </si>
 </sst>
 </file>
@@ -439,17 +475,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -465,39 +504,102 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
+      <c r="H2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="D3">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
